--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484359_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484359_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.888299999999999</v>
+        <v>9.172700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5053</v>
+        <v>6.6263</v>
       </c>
       <c r="F2" t="n">
-        <v>2.383</v>
+        <v>2.5464</v>
       </c>
       <c r="G2" t="n">
         <v>6.9923</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1695</v>
+        <v>0.4539</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1732</v>
+        <v>-0.0522</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3427</v>
+        <v>0.5061</v>
       </c>
       <c r="V2" t="n">
         <v>0.5545</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.6456</v>
+        <v>7.7777</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9431</v>
+        <v>7.3475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7025</v>
+        <v>0.4302</v>
       </c>
       <c r="G3" t="n">
         <v>4.3164</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3853</v>
+        <v>-0.2532</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9684</v>
+        <v>-0.5639</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5831</v>
+        <v>0.3108</v>
       </c>
       <c r="V3" t="n">
         <v>3.3238</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5759</v>
+        <v>4.9884</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2016</v>
+        <v>1.6558</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3743</v>
+        <v>3.3326</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4593</v>
+        <v>2.5139</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0164</v>
+        <v>1.7442</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4429</v>
+        <v>0.7696</v>
       </c>
       <c r="J4" t="n">
-        <v>3.484</v>
+        <v>1.7203</v>
       </c>
       <c r="K4" t="n">
-        <v>2.58</v>
+        <v>0.4106</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9041</v>
+        <v>1.3097</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0247</v>
+        <v>0.7936</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5636</v>
+        <v>1.3336</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5389</v>
+        <v>-0.5401</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1398</v>
+        <v>0.1657</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4404</v>
+        <v>-0.3417</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3005</v>
+        <v>0.5074</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W4" t="n">
         <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5246</v>
+        <v>4.1871</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9909</v>
+        <v>3.5949</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5337</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2702</v>
+        <v>3.4593</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6749</v>
+        <v>2.0164</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4047</v>
+        <v>1.4429</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4668</v>
+        <v>3.484</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3315</v>
+        <v>2.58</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1352</v>
+        <v>0.9041</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8035</v>
+        <v>-0.0247</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3433</v>
+        <v>-0.5636</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5399</v>
+        <v>0.5389</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>2.059</v>
+        <v>-0.249</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5009</v>
+        <v>-0.1663</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5581</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1166</v>
+        <v>3.838</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0292</v>
+        <v>1.413</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0875</v>
+        <v>2.4249</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5139</v>
+        <v>3.2672</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7442</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7696</v>
+        <v>2.5762</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7203</v>
+        <v>2.3339</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4106</v>
+        <v>-0.9171</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3097</v>
+        <v>3.2511</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7936</v>
+        <v>0.9332</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3336</v>
+        <v>1.6081</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5401</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.706</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9684</v>
+        <v>0.0558</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2623</v>
+        <v>0.5969</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.0046</v>
+        <v>3.7043</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7976</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2071</v>
+        <v>3.0979</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2672</v>
+        <v>2.2702</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6909999999999999</v>
+        <v>2.6749</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5762</v>
+        <v>-0.4047</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3339</v>
+        <v>1.4668</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9171</v>
+        <v>1.3315</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2511</v>
+        <v>0.1352</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9332</v>
+        <v>0.8035</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6081</v>
+        <v>1.3433</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5399</v>
       </c>
       <c r="P7" t="n">
         <v>0.1953</v>
@@ -1000,22 +1000,22 @@
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8194</v>
+        <v>1.2387</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4404</v>
+        <v>0.1164</v>
       </c>
       <c r="U7" t="n">
-        <v>0.379</v>
+        <v>1.1224</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2385</v>
+        <v>1.9896</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6955</v>
+        <v>1.3922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.543</v>
+        <v>0.5974</v>
       </c>
       <c r="G8" t="n">
         <v>1.5905</v>
@@ -1078,13 +1078,13 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.192</v>
+        <v>-0.4409</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0522</v>
+        <v>-0.3555</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1398</v>
+        <v>-0.0854</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3321</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1141</v>
+        <v>0.254</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4861</v>
+        <v>1.7895</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3721</v>
+        <v>-1.5355</v>
       </c>
       <c r="G9" t="n">
         <v>1.0256</v>
@@ -1156,13 +1156,13 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3924</v>
+        <v>-0.2524</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.544</v>
       </c>
       <c r="U9" t="n">
-        <v>0.455</v>
+        <v>0.2916</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4959</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3977</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1737</v>
+        <v>0.4771</v>
       </c>
       <c r="F10" t="n">
         <v>-0.5714</v>
@@ -1234,10 +1234,10 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.051</v>
+        <v>-0.7477</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1432</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7104</v>
+        <v>-1.3132</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6848</v>
+        <v>-2.2604</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9744</v>
+        <v>0.9472</v>
       </c>
       <c r="G11" t="n">
         <v>-0.569</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2548</v>
+        <v>0.1423</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6052</v>
+        <v>-0.1808</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3504</v>
+        <v>0.3232</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8865</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7624</v>
+        <v>-1.5251</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1645</v>
+        <v>-1.0634</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5979</v>
+        <v>-0.4617</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4996</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2861</v>
+        <v>-0.0488</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.044</v>
+        <v>0.0921</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2436</v>
+        <v>-2.3798</v>
       </c>
       <c r="E13" t="n">
         <v>-2.2694</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0258</v>
+        <v>-0.1104</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6816</v>
@@ -1468,13 +1468,13 @@
         <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0578</v>
+        <v>-0.194</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2448</v>
+        <v>0.1086</v>
       </c>
       <c r="V13" t="n">
         <v>0.2772</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>29.9941</v>
+        <v>30.5994</v>
       </c>
       <c r="E14" t="n">
-        <v>18.7043</v>
+        <v>19.3095</v>
       </c>
       <c r="F14" t="n">
-        <v>11.2899</v>
+        <v>11.2898</v>
       </c>
       <c r="G14" t="n">
         <v>24.9516</v>
@@ -1537,7 +1537,7 @@
         <v>-2.0283</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9068</v>
+        <v>3.906800000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-7.8136</v>
@@ -1546,10 +1546,10 @@
         <v>11.7207</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1376999999999995</v>
+        <v>0.4672999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6855</v>
+        <v>-3.0803</v>
       </c>
       <c r="U14" t="n">
         <v>3.5479</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0342</v>
+        <v>0.3417</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9415</v>
+        <v>2.7393</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9073</v>
+        <v>-2.3976</v>
       </c>
       <c r="G15" t="n">
         <v>0.863</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5385</v>
+        <v>0.8461</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.279</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6153</v>
+        <v>1.1251</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3651</v>
+        <v>-0.1278</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2417</v>
+        <v>-0.1406</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1234</v>
+        <v>0.0128</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2138</v>
@@ -1702,13 +1702,13 @@
         <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3466</v>
+        <v>-0.1094</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3026</v>
+        <v>-0.2015</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.044</v>
+        <v>0.0921</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0961</v>
+        <v>-0.8316</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3814</v>
+        <v>-0.2803</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7147</v>
+        <v>-0.5513</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3397</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.389</v>
+        <v>-0.1245</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4237</v>
+        <v>-0.3225</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0346</v>
+        <v>0.1981</v>
       </c>
       <c r="V17" t="n">
         <v>0.6093</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3021</v>
+        <v>-1.4309</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5333</v>
+        <v>0.1745</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7687</v>
+        <v>-1.6053</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1476</v>
@@ -1858,13 +1858,13 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.268</v>
+        <v>0.6032</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7125</v>
+        <v>-0.0047</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4445</v>
+        <v>0.6079</v>
       </c>
       <c r="V18" t="n">
         <v>0.3321</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9144</v>
+        <v>-3.2371</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.455</v>
+        <v>-0.8595</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4594</v>
+        <v>-2.3777</v>
       </c>
       <c r="G19" t="n">
         <v>-4.3038</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3792</v>
+        <v>0.0565</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1048</v>
+        <v>-0.2997</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2744</v>
+        <v>0.3561</v>
       </c>
       <c r="V19" t="n">
         <v>0.0335</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6018</v>
+        <v>-5.5902</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3541</v>
+        <v>-3.1518</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2478</v>
+        <v>-2.4384</v>
       </c>
       <c r="G20" t="n">
         <v>-5.8085</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7682</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1967</v>
+        <v>-0.9944</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4285</v>
+        <v>0.2378</v>
       </c>
       <c r="V20" t="n">
         <v>0.9749</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.98</v>
+        <v>-5.7274</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5994</v>
+        <v>-2.9927</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3806</v>
+        <v>-2.7347</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4976</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1839</v>
+        <v>0.0688</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2434</v>
+        <v>-0.6367</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0596</v>
+        <v>0.7055</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5172</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2728</v>
+        <v>-6.2027</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1281</v>
+        <v>-2.3304</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1447</v>
+        <v>-3.8723</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7559</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4099</v>
+        <v>-0.3398</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3548</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0551</v>
+        <v>0.2173</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1303</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4755</v>
+        <v>-7.1677</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5178</v>
+        <v>-4.4278</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9577</v>
+        <v>-2.7399</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7273</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5856</v>
+        <v>-0.1065</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6578000000000001</v>
+        <v>-0.2522</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0722</v>
+        <v>0.1457</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5758</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-29.9736</v>
+        <v>-29.9737</v>
       </c>
       <c r="E24" t="n">
         <v>-11.2693</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.7043</v>
+        <v>-18.7044</v>
       </c>
       <c r="G24" t="n">
         <v>-24.9312</v>
@@ -2326,10 +2326,10 @@
         <v>7.813700000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1376999999999999</v>
+        <v>0.1377999999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.5479</v>
+        <v>-3.5477</v>
       </c>
       <c r="U24" t="n">
         <v>3.6856</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484359_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484359_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,31 +985,31 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7043</v>
+        <v>2.4833</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6064000000000001</v>
+        <v>-0.6146</v>
       </c>
       <c r="F7" t="n">
         <v>3.0979</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2702</v>
+        <v>1.0493</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6749</v>
+        <v>2.0609</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4047</v>
+        <v>-1.0116</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4668</v>
+        <v>0.2458</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3315</v>
+        <v>0.7176</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1352</v>
+        <v>-0.4718</v>
       </c>
       <c r="M7" t="n">
         <v>0.8035</v>
@@ -1016,6 +1046,11 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.254</v>
+        <v>1.221</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7895</v>
+        <v>1.221</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5355</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0256</v>
+        <v>1.221</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9174</v>
+        <v>0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9429</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3335</v>
+        <v>1.221</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3901</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9433</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3079</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3075</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2524</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.544</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2916</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>J. SERRA SÀNCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4771</v>
+        <v>0.607</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5714</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2664</v>
+        <v>0.607</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1481</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4145</v>
+        <v>0.607</v>
       </c>
       <c r="J10" t="n">
-        <v>3.035</v>
+        <v>0.607</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0246</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0105</v>
+        <v>0.607</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7685999999999999</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1727</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7477</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6045</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1432</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3132</v>
+        <v>0.254</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2604</v>
+        <v>1.7895</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9472</v>
+        <v>-1.5355</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.569</v>
+        <v>1.0256</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1371</v>
+        <v>-0.9174</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4319</v>
+        <v>1.9429</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1029</v>
+        <v>2.3335</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3457</v>
+        <v>0.3901</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2428</v>
+        <v>1.9433</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5338000000000001</v>
+        <v>-1.3079</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2085</v>
+        <v>-1.3075</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6747</v>
+        <v>-0.0004</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1423</v>
+        <v>-0.2524</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1808</v>
+        <v>-0.544</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3232</v>
+        <v>0.2916</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8865</v>
+        <v>-1.4959</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8865</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5251</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0634</v>
+        <v>0.4771</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4617</v>
+        <v>-0.5714</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4996</v>
+        <v>2.2664</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8235</v>
+        <v>-0.1481</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3239</v>
+        <v>2.4145</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0543</v>
+        <v>3.035</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.0246</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0543</v>
+        <v>2.0105</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5538</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8235</v>
+        <v>-1.1727</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2696</v>
+        <v>0.4041</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0488</v>
+        <v>-0.7477</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.141</v>
+        <v>-0.6045</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0921</v>
+        <v>-0.1432</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3798</v>
+        <v>-1.3132</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2694</v>
+        <v>-2.2604</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1104</v>
+        <v>0.9472</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6816</v>
+        <v>-0.569</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6275</v>
+        <v>-0.1371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0541</v>
+        <v>-0.4319</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2673</v>
+        <v>-1.1029</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3482</v>
+        <v>-1.3457</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0809</v>
+        <v>0.2428</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4144</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2793</v>
+        <v>1.2085</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.135</v>
+        <v>-0.6747</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.194</v>
+        <v>0.1423</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3026</v>
+        <v>-0.1808</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1086</v>
+        <v>0.3232</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2772</v>
+        <v>-0.8865</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,229 +1566,240 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.5994</v>
+        <v>-2.1321</v>
       </c>
       <c r="E14" t="n">
-        <v>19.3095</v>
+        <v>-1.6704</v>
       </c>
       <c r="F14" t="n">
-        <v>11.2898</v>
+        <v>-0.4617</v>
       </c>
       <c r="G14" t="n">
-        <v>24.9516</v>
+        <v>-1.1065</v>
       </c>
       <c r="H14" t="n">
-        <v>6.741100000000001</v>
+        <v>-0.8235</v>
       </c>
       <c r="I14" t="n">
-        <v>18.2103</v>
+        <v>-0.2831</v>
       </c>
       <c r="J14" t="n">
-        <v>25.8258</v>
+        <v>-0.5527</v>
       </c>
       <c r="K14" t="n">
-        <v>5.587000000000001</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>20.2387</v>
+        <v>-0.5527</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8743000000000002</v>
+        <v>-0.5538</v>
       </c>
       <c r="N14" t="n">
-        <v>1.153699999999999</v>
+        <v>-0.8235</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0283</v>
+        <v>0.2696</v>
       </c>
       <c r="P14" t="n">
-        <v>3.906800000000001</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.8136</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>11.7207</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4672999999999999</v>
+        <v>-0.0488</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.0803</v>
+        <v>-0.141</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5479</v>
+        <v>0.0921</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2735</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.3778</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1043</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3417</v>
+        <v>-2.3798</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7393</v>
+        <v>-2.2694</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3976</v>
+        <v>-0.1104</v>
       </c>
       <c r="G15" t="n">
-        <v>0.863</v>
+        <v>-1.6816</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1287</v>
+        <v>-1.6275</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.2657</v>
+        <v>-0.0541</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7298</v>
+        <v>-1.2673</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6224</v>
+        <v>-1.3482</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1074</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8668</v>
+        <v>-0.4144</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4937</v>
+        <v>-0.2793</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.3731</v>
+        <v>-0.135</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8461</v>
+        <v>-0.194</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.279</v>
+        <v>-0.3026</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1251</v>
+        <v>0.1086</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1278</v>
+        <v>30.5994</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1406</v>
+        <v>19.3095</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0128</v>
+        <v>11.2898</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2138</v>
+        <v>24.9518</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1192</v>
+        <v>6.741100000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0946</v>
+        <v>18.2104</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0609</v>
+        <v>25.82579999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0205</v>
+        <v>5.5871</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>20.2387</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2747</v>
+        <v>-0.8743000000000003</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1397</v>
+        <v>1.153699999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.135</v>
+        <v>-2.0283</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>3.9068</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-7.8136</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>11.7207</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1094</v>
+        <v>0.4672999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2015</v>
+        <v>-3.0803</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0921</v>
+        <v>3.5479</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2735</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.3778</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.1043</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8316</v>
+        <v>2.1279</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2803</v>
+        <v>2.1279</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5513</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3397</v>
+        <v>2.1279</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3888</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7286</v>
+        <v>1.821</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4097</v>
+        <v>2.1279</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3287</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0809</v>
+        <v>1.821</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7494</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0601</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8095</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3225</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1981</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4309</v>
+        <v>0.3417</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1745</v>
+        <v>2.7393</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6053</v>
+        <v>-2.3976</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1476</v>
+        <v>0.863</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0834</v>
+        <v>3.1287</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0641</v>
+        <v>-2.2657</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1792</v>
+        <v>4.7298</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0844</v>
+        <v>3.6224</v>
       </c>
       <c r="L18" t="n">
-        <v>0.09470000000000001</v>
+        <v>1.1074</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.3267</v>
+        <v>-3.8668</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1678</v>
+        <v>-0.4937</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1589</v>
+        <v>-3.3731</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6032</v>
+        <v>0.8461</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0047</v>
+        <v>-0.279</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6079</v>
+        <v>1.1251</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2371</v>
+        <v>-0.1278</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8595</v>
+        <v>-0.1406</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3777</v>
+        <v>0.0128</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.3038</v>
+        <v>-0.2138</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9031</v>
+        <v>-0.1192</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4007</v>
+        <v>-0.0946</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.837</v>
+        <v>0.0609</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4045</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5675</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4668</v>
+        <v>-0.2747</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4986</v>
+        <v>-0.1397</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.9682</v>
+        <v>-0.135</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0565</v>
+        <v>-0.1094</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2997</v>
+        <v>-0.2015</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3561</v>
+        <v>0.0921</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0335</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2437</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5902</v>
+        <v>-0.8316</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1518</v>
+        <v>-0.2803</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4384</v>
+        <v>-0.5513</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.8085</v>
+        <v>-0.3397</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1934</v>
+        <v>0.3888</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.6151</v>
+        <v>-0.7286</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.6765</v>
+        <v>0.4097</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4902</v>
+        <v>0.3287</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1863</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.132</v>
+        <v>-0.7494</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7032</v>
+        <v>0.0601</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.4287</v>
+        <v>-0.8095</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.1245</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9944</v>
+        <v>-0.3225</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2378</v>
+        <v>0.1981</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9749</v>
+        <v>0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.521</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7274</v>
+        <v>-1.4309</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9927</v>
+        <v>0.1745</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7347</v>
+        <v>-1.6053</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4976</v>
+        <v>-3.1476</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0097</v>
+        <v>-1.0834</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.5073</v>
+        <v>-2.0641</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0392</v>
+        <v>0.1792</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.0844</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5389</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.5368</v>
+        <v>-3.3267</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5684</v>
+        <v>-1.1678</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9684</v>
+        <v>-2.1589</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0688</v>
+        <v>0.6032</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6367</v>
+        <v>-0.0047</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7055</v>
+        <v>0.6079</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5172</v>
+        <v>0.3321</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0754</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2027</v>
+        <v>-3.2371</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3304</v>
+        <v>-0.8595</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8723</v>
+        <v>-2.3777</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7559</v>
+        <v>-4.3038</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2062</v>
+        <v>-1.9031</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5497</v>
+        <v>-2.4007</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1801</v>
+        <v>-0.837</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1663</v>
+        <v>-1.4045</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0138</v>
+        <v>0.5675</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.936</v>
+        <v>-3.4668</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3725</v>
+        <v>-0.4986</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.5636</v>
+        <v>-2.9682</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3398</v>
+        <v>0.0565</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.2997</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2173</v>
+        <v>0.3561</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1303</v>
+        <v>0.0335</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1303</v>
+        <v>-0.2437</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1677</v>
+        <v>-5.5902</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4278</v>
+        <v>-3.1518</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7399</v>
+        <v>-2.4384</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.7273</v>
+        <v>-5.8085</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.7425</v>
+        <v>-2.1934</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9848</v>
+        <v>-3.6151</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1906</v>
+        <v>-2.6765</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.0392</v>
+        <v>-1.4902</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8486</v>
+        <v>-1.1863</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.5366</v>
+        <v>-3.132</v>
       </c>
       <c r="N23" t="n">
         <v>-0.7032</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.8334</v>
+        <v>-2.4287</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1065</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2522</v>
+        <v>-0.9944</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1457</v>
+        <v>0.2378</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5758</v>
+        <v>0.9749</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0549</v>
+        <v>1.4959</v>
       </c>
       <c r="X23" t="n">
         <v>-0.521</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-5.7274</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.9927</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.7347</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3.4976</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.5073</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5389</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-3.5368</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.5684</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-2.9684</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.6367</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.7055</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.5172</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.4418</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.0754</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D. CAJAL PENACHO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.2027</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.3304</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-3.8723</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.7559</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.2062</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.5497</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.936</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.3725</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-2.5636</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.3398</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.5570000000000001</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.1303</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.1303</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R. DIAZ DEL VALLE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-9.2956</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-6.5558</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.7399</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-6.8552</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-4.0495</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.8058</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-3.3186</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-3.3462</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-3.5366</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7032</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-2.8334</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.1065</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.2522</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.5758</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.521</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484359_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-29.9737</v>
       </c>
-      <c r="E24" t="n">
-        <v>-11.2693</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="E27" t="n">
+        <v>-11.2694</v>
+      </c>
+      <c r="F27" t="n">
         <v>-18.7044</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>-24.9312</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H27" t="n">
         <v>-6.720599999999999</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I27" t="n">
         <v>-18.2106</v>
       </c>
-      <c r="J24" t="n">
-        <v>0.8948000000000003</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-1.133500000000001</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="J27" t="n">
+        <v>0.8947000000000003</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.1335</v>
+      </c>
+      <c r="L27" t="n">
         <v>2.0282</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>-25.8258</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>-5.587</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>-20.2388</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>-3.9069</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>7.813700000000001</v>
       </c>
-      <c r="S24" t="n">
-        <v>0.1377999999999998</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="S27" t="n">
+        <v>0.1377999999999999</v>
+      </c>
+      <c r="T27" t="n">
         <v>-3.5477</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>3.6856</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>-1.2735</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>3.1043</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-4.3779</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
